--- a/error_models/conv_models/nv_16x32_b1_dat-524288_wt-131072_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_16x32_b1_dat-524288_wt-131072_int8/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9851354888382566</v>
+        <v>0.9881777160483918</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0148581448920612</v>
+        <v>0.011817175929011</v>
       </c>
       <c r="I2" t="n">
-        <v>6.327360672714084e-06</v>
+        <v>5.069113587763896e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.8978736600066799</v>
@@ -579,7 +709,7 @@
         <v>0.028559415249184</v>
       </c>
       <c r="P2" t="n">
-        <v>1.175944155154004e-06</v>
+        <v>1.175944155154005e-06</v>
       </c>
       <c r="Q2" t="n">
         <v>0.00412082733365</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.2019333436979947</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7980666563020052</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -616,16 +824,16 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9924122035900038</v>
+        <v>0.9935259986674254</v>
       </c>
       <c r="H3" t="n">
-        <v>0.007580498538457</v>
+        <v>0.0064678083636685</v>
       </c>
       <c r="I3" t="n">
-        <v>7.258962529884813e-06</v>
+        <v>6.154059896969657e-06</v>
       </c>
       <c r="J3" t="n">
-        <v>0.709842767292243</v>
+        <v>0.7098427672922428</v>
       </c>
       <c r="K3" t="n">
         <v>0.1987641561578149</v>
@@ -646,7 +854,7 @@
         <v>2.337007341448756e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.152450580483099e-05</v>
+        <v>7.1524505804831e-05</v>
       </c>
       <c r="R3" t="n">
         <v>0.0001482133960401</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>0.0001906948457596</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.2019327705072294</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.7980672294927705</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -680,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9986390561701414</v>
+        <v>0.9988018193355324</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0013535402369606</v>
+        <v>0.001191624246482</v>
       </c>
       <c r="I4" t="n">
-        <v>7.364683888761173e-06</v>
+        <v>6.51750897633355e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.1727806885040053</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7341798847579364</v>
+        <v>0.7341798847579365</v>
       </c>
       <c r="L4" t="n">
         <v>0.0274959179399751</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>0.0004445319200864</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9994732971841078</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.0005267028158922</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.2019332928598753</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.7980667071401245</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -744,13 +1108,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9961820516432914</v>
+        <v>0.9966725700341812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003810503916745</v>
+        <v>0.0033208441809578</v>
       </c>
       <c r="I5" t="n">
-        <v>7.405530954312462e-06</v>
+        <v>6.546875851745031e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.3866829917275161</v>
@@ -771,7 +1135,7 @@
         <v>0.029815612449124</v>
       </c>
       <c r="P5" t="n">
-        <v>7.140905814423908e-07</v>
+        <v>7.140905814423909e-07</v>
       </c>
       <c r="Q5" t="n">
         <v>1.014043165879909e-05</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0007918944079409</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.9994727322543804</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.0005272677456196</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.2019480810514047</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7980519189485953</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -808,19 +1250,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9975886661895316</v>
+        <v>0.9977783638754516</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0024037910550114</v>
+        <v>0.0022149408928684</v>
       </c>
       <c r="I6" t="n">
-        <v>7.503846447550095e-06</v>
+        <v>6.656322670715146e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.154636383620655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7510626474382819</v>
+        <v>0.7510626474382818</v>
       </c>
       <c r="L6" t="n">
         <v>0.0191887523133633</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0011352216693034</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9994518406929668</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.0005481593070332</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.1999787543933492</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8000212456066508</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -872,16 +1392,16 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9806651966475248</v>
+        <v>0.987187942766232</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0193276229824078</v>
+        <v>0.0128060701774544</v>
       </c>
       <c r="I7" t="n">
-        <v>7.141461057877378e-06</v>
+        <v>5.948147304139923e-06</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8978779141132057</v>
+        <v>0.8978779141132056</v>
       </c>
       <c r="K7" t="n">
         <v>0.0204426673135882</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>5.00822431524772e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.2019483281726442</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.7980516718273557</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -936,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9925621826704631</v>
+        <v>0.9947898657289558</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0074305385038761</v>
+        <v>0.0052039899642497</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2399166515685e-06</v>
+        <v>6.105397785242423e-06</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8484197222301399</v>
+        <v>0.8484197222301398</v>
       </c>
       <c r="K8" t="n">
         <v>0.0618395893874329</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0023664003273838</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2019330225614654</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7980669774385345</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9968913854502772</v>
+        <v>0.9985733728197608</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0031005033678093</v>
+        <v>0.0014194966893189</v>
       </c>
       <c r="I9" t="n">
-        <v>8.072272904157585e-06</v>
+        <v>7.091581910912213e-06</v>
       </c>
       <c r="J9" t="n">
         <v>0.8026109205957072</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>5.046663594734095e-07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1064,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9992459205988438</v>
+        <v>0.9992821707438978</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0007467347204988</v>
+        <v>0.0007112140964976</v>
       </c>
       <c r="I10" t="n">
-        <v>7.305771648068015e-06</v>
+        <v>6.576250595339328e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0038839048142468</v>
@@ -1085,7 +1839,7 @@
         <v>0.002148476200423</v>
       </c>
       <c r="N10" t="n">
-        <v>5.58280234098339e-06</v>
+        <v>5.582802340983391e-06</v>
       </c>
       <c r="O10" t="n">
         <v>3.330404696980181e-07</v>
@@ -1103,6 +1857,84 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9995947937784539</v>
+        <v>0.9997005420846884</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003976690350824</v>
+        <v>0.0002927624474871</v>
       </c>
       <c r="I11" t="n">
-        <v>7.498277454523808e-06</v>
+        <v>6.656558815071929e-06</v>
       </c>
       <c r="J11" t="n">
         <v>0.0572545404299128</v>
@@ -1167,6 +1999,84 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9984902287582182</v>
+        <v>0.999061865025716</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0015018317218406</v>
+        <v>0.0009310246467179</v>
       </c>
       <c r="I12" t="n">
-        <v>7.900610931837911e-06</v>
+        <v>7.071418556977674e-06</v>
       </c>
       <c r="J12" t="n">
         <v>0.3251367917414526</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>0.0008182320043168</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.99864670087592</v>
+        <v>0.9994664091772376</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0013453234348719</v>
+        <v>0.0005266065074097</v>
       </c>
       <c r="I13" t="n">
-        <v>7.93678019891429e-06</v>
+        <v>6.94540634331095e-06</v>
       </c>
       <c r="J13" t="n">
         <v>0.4913115573177118</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9978608626127716</v>
+        <v>0.9986470662879968</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0021310995946025</v>
+        <v>0.0013456890289968</v>
       </c>
       <c r="I14" t="n">
-        <v>7.99888361660364e-06</v>
+        <v>7.205773997050736e-06</v>
       </c>
       <c r="J14" t="n">
         <v>0.4939048917266898</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>0.0004565105170461</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.99833805033414</v>
+        <v>0.9992243395805324</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0016540488097524</v>
+        <v>0.000768758413683</v>
       </c>
       <c r="I15" t="n">
-        <v>7.861947098353529e-06</v>
+        <v>6.863096775251543e-06</v>
       </c>
       <c r="J15" t="n">
         <v>0.4844039633824602</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.999579345839342</v>
+        <v>0.999780387795716</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0004131511548131</v>
+        <v>0.000213117606233</v>
       </c>
       <c r="I16" t="n">
-        <v>7.464096835551156e-06</v>
+        <v>6.455689041578149e-06</v>
       </c>
       <c r="J16" t="n">
         <v>0.1144355077557909</v>
@@ -1475,7 +2697,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8659942269848211</v>
+        <v>0.8659942269848213</v>
       </c>
       <c r="Q16" t="n">
         <v>4.581248015075673e-05</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9992260935865576</v>
+        <v>0.999360086653065</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000766353924896</v>
+        <v>0.0006331194659422</v>
       </c>
       <c r="I17" t="n">
-        <v>7.513579537388488e-06</v>
+        <v>6.754971983558937e-06</v>
       </c>
       <c r="J17" t="n">
         <v>0.0581208387129584</v>
@@ -1539,7 +2839,7 @@
         <v>4.033502730019764e-08</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8596940993099665</v>
+        <v>0.8596940993099664</v>
       </c>
       <c r="Q17" t="n">
         <v>0.0624782290396329</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0019164977430463</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1576,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9994217748554086</v>
+        <v>0.9996922657294962</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0005707327280059</v>
+        <v>0.0003012484105292</v>
       </c>
       <c r="I18" t="n">
-        <v>7.453507576274757e-06</v>
+        <v>6.446950965262353e-06</v>
       </c>
       <c r="J18" t="n">
         <v>0.1271206359223226</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>2.753233015576455e-07</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1640,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9993753245772952</v>
+        <v>0.9994239587881696</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0006172778191012</v>
+        <v>0.0005694054521967</v>
       </c>
       <c r="I19" t="n">
-        <v>7.358694594374414e-06</v>
+        <v>6.596850624366968e-06</v>
       </c>
       <c r="J19" t="n">
         <v>0.0031178201600597</v>
@@ -1679,6 +3135,84 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9997365420545624</v>
+        <v>0.9997895519504754</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0002561564585283</v>
+        <v>0.0002040396850785</v>
       </c>
       <c r="I20" t="n">
-        <v>7.262577899920744e-06</v>
+        <v>6.369455436740023e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0001358731623115</v>
@@ -1743,6 +3277,84 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9988811781202248</v>
+        <v>0.9989794895361448</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0011114772030096</v>
+        <v>0.0010138982771409</v>
       </c>
       <c r="I21" t="n">
-        <v>7.305767756388752e-06</v>
+        <v>6.573277704983711e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0694706930003756</v>
@@ -1807,6 +3419,84 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0952951024069059</v>
+        <v>0.6447672496296857</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9046971666438114</v>
+        <v>0.3552257571528429</v>
       </c>
       <c r="I22" t="n">
-        <v>7.69204027338176e-06</v>
+        <v>6.954308462306886e-06</v>
       </c>
       <c r="J22" t="n">
         <v>0.0024355247424339</v>
@@ -1872,6 +3562,84 @@
       </c>
       <c r="T22" t="n">
         <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1896,16 +3664,16 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9832334099917056</v>
+        <v>0.9864200711266964</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0167589985523635</v>
+        <v>0.0135730682587269</v>
       </c>
       <c r="I23" t="n">
-        <v>7.552546921855431e-06</v>
+        <v>6.821705567440668e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8224639984752469</v>
+        <v>0.822463998475247</v>
       </c>
       <c r="K23" t="n">
         <v>0.0815635629646335</v>
@@ -1926,7 +3694,7 @@
         <v>1.704360397314716e-06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.0816742662467206</v>
+        <v>0.0816742662467205</v>
       </c>
       <c r="R23" t="n">
         <v>3.700529874566422e-06</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>6.604722583322409e-07</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9967484972935288</v>
+        <v>0.9977285599123732</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0032439005250719</v>
+        <v>0.0022645783599729</v>
       </c>
       <c r="I24" t="n">
-        <v>7.563272389906055e-06</v>
+        <v>6.822818644583698e-06</v>
       </c>
       <c r="J24" t="n">
         <v>0.5469520740898169</v>
@@ -1987,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>0.350908803281652</v>
+        <v>0.3509088032816519</v>
       </c>
       <c r="Q24" t="n">
         <v>0.0816376413732519</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>1.910578938077223e-06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9976423181057394</v>
+        <v>0.9979676475714974</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0023503434363984</v>
+        <v>0.0020257415649686</v>
       </c>
       <c r="I25" t="n">
-        <v>7.299548852925437e-06</v>
+        <v>6.571954524975636e-06</v>
       </c>
       <c r="J25" t="n">
         <v>0.1798417563824407</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0010452921899798</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9982757068543237</v>
+        <v>0.9984628955443136</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0017167801382159</v>
+        <v>0.0015304024187857</v>
       </c>
       <c r="I26" t="n">
-        <v>7.474098451258742e-06</v>
+        <v>6.663127891320293e-06</v>
       </c>
       <c r="J26" t="n">
         <v>0.1505168541347569</v>
@@ -2115,7 +4117,7 @@
         <v>0.0469818391953718</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7508244867181055</v>
+        <v>0.7508244867181054</v>
       </c>
       <c r="Q26" t="n">
         <v>3.300307612734215e-05</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0035256705047281</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.9990964667964468</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.0009035332035531</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.2019334181358832</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.7980665818641168</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9923982046904239</v>
+        <v>0.9944214637643762</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0075947718053165</v>
+        <v>0.005572668879219</v>
       </c>
       <c r="I27" t="n">
-        <v>6.984595250118106e-06</v>
+        <v>5.828447395563268e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.8681347357810822</v>
@@ -2192,6 +4272,84 @@
       </c>
       <c r="T27" t="n">
         <v>1.295839159761482e-06</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.2019331790972746</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.7980668209027254</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9972089679797193</v>
+        <v>0.9977918179539456</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0027836893321633</v>
+        <v>0.0022018079934427</v>
       </c>
       <c r="I28" t="n">
-        <v>7.303779108285024e-06</v>
+        <v>6.335143602437434e-06</v>
       </c>
       <c r="J28" t="n">
         <v>0.5000965774928482</v>
@@ -2243,10 +4401,10 @@
         <v>0.0244805979075358</v>
       </c>
       <c r="P28" t="n">
-        <v>0.3981556321204358</v>
+        <v>0.3981556321204359</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.038753383439384e-05</v>
+        <v>4.038753383439385e-05</v>
       </c>
       <c r="R28" t="n">
         <v>2.207932597847146e-06</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0006499004843073</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.9991039704837336</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.0008960295162664</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9942587886936276</v>
+        <v>0.9946928799393506</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0057339547255504</v>
+        <v>0.0053008227881279</v>
       </c>
       <c r="I29" t="n">
-        <v>7.217671812897468e-06</v>
+        <v>6.258363512196338e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.3589193369306667</v>
@@ -2307,7 +4543,7 @@
         <v>0.027200090177287</v>
       </c>
       <c r="P29" t="n">
-        <v>0.5401583468669359</v>
+        <v>0.540158346866936</v>
       </c>
       <c r="Q29" t="n">
         <v>0.0016313125206054</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0035061046310999</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.999271923304172</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.0007280766958278</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2344,19 +4658,19 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0946476922765344</v>
+        <v>0.6443076758288035</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9053446014027512</v>
+        <v>0.3556853348888049</v>
       </c>
       <c r="I30" t="n">
-        <v>7.667411705198031e-06</v>
+        <v>6.9503733821338e-06</v>
       </c>
       <c r="J30" t="n">
         <v>0.0016394532230402</v>
       </c>
       <c r="K30" t="n">
-        <v>0.9959553800532484</v>
+        <v>0.9959553800532482</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -2384,6 +4698,84 @@
       </c>
       <c r="T30" t="n">
         <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2408,16 +4800,16 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9898192906551516</v>
+        <v>0.9939755423848524</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0101726181404206</v>
+        <v>0.0060171083580196</v>
       </c>
       <c r="I31" t="n">
-        <v>8.052295418596522e-06</v>
+        <v>7.310348118806242e-06</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4509450676984662</v>
+        <v>0.4509450676984661</v>
       </c>
       <c r="K31" t="n">
         <v>0.041596226187862</v>
@@ -2429,10 +4821,10 @@
         <v>0.0061913943467231</v>
       </c>
       <c r="N31" t="n">
-        <v>3.406728914579475e-06</v>
+        <v>3.406728914579476e-06</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4293166336268697</v>
+        <v>0.4293166336268696</v>
       </c>
       <c r="P31" t="n">
         <v>2.478279227694715e-06</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>8.618060175936824e-06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,19 +4942,19 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9851352168956606</v>
+        <v>0.9905139015308624</v>
       </c>
       <c r="H32" t="n">
-        <v>0.014857249673607</v>
+        <v>0.0094793197786166</v>
       </c>
       <c r="I32" t="n">
-        <v>7.494521723030869e-06</v>
+        <v>6.739781511802802e-06</v>
       </c>
       <c r="J32" t="n">
         <v>0.5258477203980684</v>
       </c>
       <c r="K32" t="n">
-        <v>0.3868617516982159</v>
+        <v>0.3868617516982158</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2493,7 +4963,7 @@
         <v>0.013254692704154</v>
       </c>
       <c r="N32" t="n">
-        <v>2.206275965528297e-06</v>
+        <v>2.206275965528296e-06</v>
       </c>
       <c r="O32" t="n">
         <v>5.111380230066542e-06</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>0.0012039212827325</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9857141369756536</v>
+        <v>0.9863919826342769</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0142787552168907</v>
+        <v>0.0136021390843382</v>
       </c>
       <c r="I33" t="n">
-        <v>7.068898446364334e-06</v>
+        <v>5.839372375727016e-06</v>
       </c>
       <c r="J33" t="n">
         <v>0.3532184806271804</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0.0100060221857886</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.9994536766782788</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0.0005463233217211</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9835058581793752</v>
+        <v>0.9845253570662552</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0164872121221776</v>
+        <v>0.0154689679693834</v>
       </c>
       <c r="I34" t="n">
-        <v>6.890789437927652e-06</v>
+        <v>5.636055351881461e-06</v>
       </c>
       <c r="J34" t="n">
         <v>0.3039445512970741</v>
@@ -2627,7 +5253,7 @@
         <v>0.0690518795982468</v>
       </c>
       <c r="P34" t="n">
-        <v>1.971855200304359e-06</v>
+        <v>1.97185520030436e-06</v>
       </c>
       <c r="Q34" t="n">
         <v>4.518104327050857e-05</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>0.008060402405563801</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9800358732249335</v>
+        <v>0.9874182876200615</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0199571488793424</v>
+        <v>0.01257593579756925</v>
       </c>
       <c r="I35" t="n">
-        <v>6.93898671498774e-06</v>
+        <v>5.737673359925191e-06</v>
       </c>
       <c r="J35" t="n">
         <v>0.8978739355267571</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>5.461907431087323e-07</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.2019329008855767</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0.7980670991144233</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9694637348549902</v>
+        <v>0.9766840285992713</v>
       </c>
       <c r="H36" t="n">
-        <v>0.03052934363234375</v>
+        <v>0.0233102056541522</v>
       </c>
       <c r="I36" t="n">
-        <v>6.882603656780596e-06</v>
+        <v>5.726837567246352e-06</v>
       </c>
       <c r="J36" t="n">
         <v>0.8744493082192958</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>9.914066748336348e-05</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2792,19 +5652,19 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9894347454235255</v>
+        <v>0.9906699031436099</v>
       </c>
       <c r="H37" t="n">
-        <v>0.010558198326389</v>
+        <v>0.00932414134352785</v>
       </c>
       <c r="I37" t="n">
-        <v>7.017341076287482e-06</v>
+        <v>5.916603852904126e-06</v>
       </c>
       <c r="J37" t="n">
-        <v>0.6017147337606196</v>
+        <v>0.6017147337606197</v>
       </c>
       <c r="K37" t="n">
-        <v>0.299558391340323</v>
+        <v>0.2995583913403231</v>
       </c>
       <c r="L37" t="n">
         <v>0.05611676158934655</v>
@@ -2813,7 +5673,7 @@
         <v>0.01706618553673835</v>
       </c>
       <c r="N37" t="n">
-        <v>0.01580385345456685</v>
+        <v>0.0158038534545669</v>
       </c>
       <c r="O37" t="n">
         <v>0.0066056728505106</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.000227919463662541</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9910737221030383</v>
+        <v>0.9919245395380444</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00891883810565345</v>
+        <v>0.00806897234835985</v>
       </c>
       <c r="I38" t="n">
-        <v>7.400882298632918e-06</v>
+        <v>6.449204586568105e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.2954563668587841</v>
@@ -2883,7 +5821,7 @@
         <v>0.0084149007929602</v>
       </c>
       <c r="P38" t="n">
-        <v>0.6044758878028396</v>
+        <v>0.6044758878028397</v>
       </c>
       <c r="Q38" t="n">
         <v>0.000466877921746156</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.0002322353524451</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.999455782158991</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.0005442178410089001</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9939027531285209</v>
+        <v>0.9942283651970449</v>
       </c>
       <c r="H39" t="n">
-        <v>0.006089901733858925</v>
+        <v>0.005765097130243924</v>
       </c>
       <c r="I39" t="n">
-        <v>7.306228610683294e-06</v>
+        <v>6.498763701987675e-06</v>
       </c>
       <c r="J39" t="n">
         <v>0.07995647234906135</v>
@@ -2947,7 +5963,7 @@
         <v>0.02686170286618115</v>
       </c>
       <c r="P39" t="n">
-        <v>0.6228356467426125</v>
+        <v>0.6228356467426124</v>
       </c>
       <c r="Q39" t="n">
         <v>0.0004894447134925654</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.00286665968688445</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.749637801332948</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.00036219866705195</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0.1514537890296694</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0.5985462109703306</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9976720993622676</v>
+        <v>0.9978572495788364</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00232038518045975</v>
+        <v>0.00213603922106455</v>
       </c>
       <c r="I40" t="n">
-        <v>7.47654826335521e-06</v>
+        <v>6.672291089643319e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.1172346739295082</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.0021898262589983</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.4995460822542603</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.0004539177457397</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0.1009666931664185</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0.3990333068335815</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_16x32_b1_dat-524288_wt-131072_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_16x32_b1_dat-524288_wt-131072_int8/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,345 +425,350 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9881777160483918</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.011817175929011</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>5.069113587763896e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.8978736600066799</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0286275214770736</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0326405390523412</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>1.129933714113147e-05</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.008163717091722899</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.028559415249184</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>1.175944155154005e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.00412082733365</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>4.740805307591896e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>1.331518511777042e-06</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
         <v>0.2019333436979947</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AD2" t="n">
         <v>0.7980666563020052</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -775,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -790,87 +795,93 @@
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9935259986674254</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0064678083636685</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>6.154059896969657e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.7098427672922428</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.1987641561578149</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.071423827662702</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.00912020816198</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0043738565481058</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0058284611836326</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>2.337007341448756e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>7.1524505804831e-05</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>0.0001482133960401</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0002339143295662</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.0001906948457596</v>
       </c>
-      <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
@@ -884,22 +895,22 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.2019327705072294</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>0.7980672294927705</v>
       </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
       <c r="AE3" t="n">
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -911,19 +922,19 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="n">
         <v>1</v>
@@ -932,116 +943,122 @@
         <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.9988018193355324</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.001191624246482</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>6.51750897633355e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.1727806885040053</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.7341798847579365</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0274959179399751</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.009771648898791599</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0204047377292251</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0305999987388161</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>9.834862165808018e-07</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>2.881709740637702e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0034037878486255</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.000888964169906</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.0004445319200864</v>
       </c>
-      <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
         <v>0.9994732971841078</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.0005267028158922</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
       <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0.2019332928598753</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.7980667071401245</v>
       </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
@@ -1053,19 +1070,19 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1074,116 +1091,122 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9966725700341812</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0033208441809578</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>6.546875851745031e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.3866829917275161</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.5148798540714313</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.034939046349977</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0131124731597488</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0172664354899967</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.029815612449124</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>7.140905814423909e-07</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>1.014043165879909e-05</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0020429442148739</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0004578546981413</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0007918944079409</v>
       </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
       <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
         <v>0.9994727322543804</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>0.0005272677456196</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
       <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.2019480810514047</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>0.7980519189485953</v>
       </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1195,19 +1218,19 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="n">
         <v>1</v>
@@ -1216,116 +1239,122 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9977783638754516</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0022149408928684</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>6.656322670715146e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.154636383620655</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.7510626474382818</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.0191887523133633</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.008191100719479</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0502199968458123</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0125543770386346</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>4.56959647774287e-07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>2.084175393478797e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0029899804827996</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>2.022490788407931e-07</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0011352216693034</v>
       </c>
-      <c r="U6" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.9994518406929668</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.0005481593070332</v>
       </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
       <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.1999787543933492</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>0.8000212456066508</v>
       </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1337,19 +1366,19 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
@@ -1358,122 +1387,128 @@
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.987187942766232</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0128060701774544</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>5.948147304139923e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.8978779141132056</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.0204426673135882</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.008163967825782799</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>1.114277470470096e-05</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0367234544570295</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0203996701569261</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>3.039624179341304e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0163761549629804</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>1.806809166472151e-07</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>1.268359245704602e-06</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>5.00822431524772e-07</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.2019483281726442</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.7980516718273557</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE7" t="n">
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1485,13 +1520,13 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
         <v>1</v>
@@ -1500,116 +1535,122 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9947898657289558</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0052039899642497</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>6.105397785242423e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.8484197222301398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0618395893874329</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0307492539852022</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0080591597524743</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0201071157662743</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0189215526937379</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>2.417923202219741e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0095218745449563</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>3.28132047511675e-06</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>9.593159711536117e-06</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0023664003273838</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.2019330225614654</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.7980669774385345</v>
       </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
       <c r="AE8" t="n">
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1621,19 +1662,19 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1642,101 +1683,107 @@
         <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9985733728197608</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0014194966893189</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>7.091581910912213e-06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.8026109205957072</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.1136122456798652</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>1.256282896967401e-07</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.0020742901803337</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>3.977791218857249e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>4.67849601200276e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.0816810157720555</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>2.891108044759526e-06</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>9.311173104347023e-06</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>5.046663594734095e-07</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1751,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1769,13 +1816,13 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
@@ -1784,101 +1831,107 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9992821707438978</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0007112140964976</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>6.576250595339328e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0038839048142468</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.9249101694155404</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.002148476200423</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>5.582802340983391e-06</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>3.330404696980181e-07</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.06530986422161481</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0037416305963551</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1893,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1911,116 +1964,122 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
         <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9997005420846884</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0002927624474871</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>6.656558815071929e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0572545404299128</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.9263664000024744</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>6.052404882088551e-06</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>5.558842326513817e-06</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>3.832417005807255e-08</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0163555908094873</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>1.178027773743239e-05</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2035,13 +2094,13 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2053,102 +2112,108 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.999061865025716</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0009310246467179</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>7.071418556977674e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.3251367917414526</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.0122909427141839</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>2.652529348236155e-06</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.5727066525129436</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.0816578834564239</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>9.122025510982836e-06</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0073776841068106</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>0.0008182320043168</v>
       </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
         <v>1</v>
       </c>
@@ -2162,7 +2227,7 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2177,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2195,13 +2260,13 @@
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2210,101 +2275,107 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9994664091772376</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0005266065074097</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>6.94540634331095e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.4913115573177118</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>5.756568582209104e-06</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>3.17315295694275e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.4555323598358311</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.0445629422902471</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>8.78056617086742e-06</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0085753913594906</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1</v>
-      </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2319,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2337,13 +2408,13 @@
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
@@ -2352,87 +2423,93 @@
         <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9986470662879968</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0013456890289968</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>7.205773997050736e-06</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.4939048917266898</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.0104808938864344</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>2.437081126791556e-06</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>7.823194418659266e-09</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.4039467749756822</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.0816537353984174</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>7.30351453188798e-06</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0095474061678674</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.0004565105170461</v>
       </c>
-      <c r="U14" t="n">
-        <v>1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
@@ -2446,7 +2523,7 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2461,13 +2538,13 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
         <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2479,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO14" t="n">
         <v>1</v>
@@ -2494,101 +2571,107 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9992243395805324</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.000768758413683</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>6.863096775251543e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.4844039633824602</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.044177485530608e-06</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>2.749810547623912e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.4627962046246403</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.0445524875394117</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>8.211082583049975e-06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0082333004738622</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1</v>
-      </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2603,13 +2686,13 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2621,13 +2704,13 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO15" t="n">
         <v>1</v>
@@ -2636,101 +2719,107 @@
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.999780387795716</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.000213117606233</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>6.455689041578149e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.1144355077557909</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>1.137021466103565e-05</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.8392473310022e-05</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>4.999653412069925e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.8659942269848213</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>4.581248015075673e-05</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>1.283499860525611e-05</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0194768165302395</v>
       </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1</v>
-      </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2745,13 +2834,13 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2763,13 +2852,13 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
@@ -2778,87 +2867,93 @@
         <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.999360086653065</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0006331194659422</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>6.754971983558937e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.0581208387129584</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0016432344483364</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>8.06195675407581e-07</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.0120300285171357</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>5.923880303679754e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>4.033502730019764e-08</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.8596940993099664</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.0624782290396329</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0008286821088982</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0032815808000096</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0019164977430463</v>
       </c>
-      <c r="U17" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
@@ -2878,7 +2973,7 @@
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2887,13 +2982,13 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2905,13 +3000,13 @@
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
@@ -2920,101 +3015,107 @@
         <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9996922657294962</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.0003012484105292</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>6.446950965262353e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.1271206359223226</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>0.0011444544760374</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>1.376616507788102e-07</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>2.494645964518641e-05</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>5.497139471984213e-06</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.8271415440362848</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.0297212541418885</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>1.25311559232229e-05</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0148286847744646</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>2.753233015576455e-07</v>
       </c>
-      <c r="U18" t="n">
-        <v>1</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3029,13 +3130,13 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -3047,13 +3148,13 @@
         <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
         <v>1</v>
@@ -3062,101 +3163,107 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9994239587881696</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0005694054521967</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>6.596850624366968e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0031178201600597</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.9266873850014324</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.001075093039245</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>5.909135606324506e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>5.665854524526069e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0680286135524116</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0010850835436904</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3171,13 +3278,13 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3189,116 +3296,122 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
         <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9997895519504754</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0002040396850785</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>6.369455436740023e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0001358731623115</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.9906742011421052</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>5.529197614064483e-06</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>5.756076299222762e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>2.729310217353423e-08</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0082150363433972</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.0009635378761613</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3313,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3331,116 +3444,122 @@
         <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9989794895361448</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0010138982771409</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>6.573277704983711e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0694706930003756</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.8541392056629149</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0017535883256711</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>5.711313511538955e-06</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>3.784727267300194e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.07141631642289981</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0032140678928909</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3455,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3473,116 +3592,122 @@
         <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6447672496296857</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3552257571528429</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>6.954308462306886e-06</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0024355247424339</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9951306118038084</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>3.885266830626201e-06</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>3.283347742400618e-08</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.016833768238772e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0024296890359295</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>1.036200864751965e-07</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>1.036200864751965e-07</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3597,13 +3722,13 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3615,13 +3740,13 @@
         <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
@@ -3630,122 +3755,128 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.9864200711266964</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.0135730682587269</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>6.821705567440668e-06</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.822463998475247</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.0815635629646335</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.0142860194079027</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>2.401897326560897e-06</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.704360397314716e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0816742662467205</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>3.700529874566422e-06</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>3.646736630120882e-06</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>6.604722583322409e-07</v>
       </c>
-      <c r="U23" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -3757,13 +3888,13 @@
         <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO23" t="n">
         <v>1</v>
@@ -3772,101 +3903,107 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9977285599123732</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0022645783599729</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>6.822818644583698e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.5469520740898169</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>2.489355024476171e-07</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.0155817701790675</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2.024038889047967e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.3509088032816519</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.0816376413732519</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>6.643267807705794e-06</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0049088453460649</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>1.910578938077223e-06</v>
       </c>
-      <c r="U24" t="n">
-        <v>1</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3881,13 +4018,13 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3899,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="n">
         <v>1</v>
@@ -3914,87 +4051,93 @@
         <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9979676475714974</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0020257415649686</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>6.571954524975636e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.1798417563824407</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0024021086387059</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.0001598236712248</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0147430687989305</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>2.481034081928981e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>8.180330791598822e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.7181528691950279</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.08163715462419099</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0008954718086696</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0011199265674075</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0010452921899798</v>
       </c>
-      <c r="U25" t="n">
-        <v>1</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>1</v>
       </c>
@@ -4014,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4023,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -4041,13 +4184,13 @@
         <v>0</v>
       </c>
       <c r="AL25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="n">
         <v>1</v>
@@ -4056,116 +4199,122 @@
         <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
         <v>0</v>
       </c>
       <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9984628955443136</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0015304024187857</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>6.663127891320293e-06</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.1505168541347569</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0016106744340896</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0228604791016752</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.008257150356788499</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0123673717994026</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0469818391953718</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.7508244867181054</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>3.300307612734215e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0014113366812056</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0016110950887393</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0035256705047281</v>
       </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
       <c r="W26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.9990964667964468</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.0009035332035531</v>
       </c>
-      <c r="Y26" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
       <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.2019334181358832</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.7980665818641168</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4177,19 +4326,19 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
         <v>1</v>
@@ -4198,116 +4347,122 @@
         <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
         <v>0</v>
       </c>
       <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9944214637643762</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.005572668879219</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>5.828447395563268e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.8681347357810822</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.0429259043809171</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.0518511211872263</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0072676345022648</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0042523565818421</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0220999605335817</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>2.212350627518582e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0034519763266804</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>3.188342983473095e-06</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>9.575264625039608e-06</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>1.295839159761482e-06</v>
       </c>
-      <c r="U27" t="n">
-        <v>1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
         <v>0.2019331790972746</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.7980668209027254</v>
       </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
       <c r="AE27" t="n">
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -4319,19 +4474,19 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -4340,116 +4495,122 @@
         <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
         <v>0</v>
       </c>
       <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9977918179539456</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0022018079934427</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>6.335143602437434e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.5000965774928482</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.053040266775016</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.0142640763853139</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0040838208587429</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0244805979075358</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.3981556321204359</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>4.038753383439385e-05</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>2.207932597847146e-06</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0051864936003582</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0006499004843073</v>
       </c>
-      <c r="U28" t="n">
-        <v>1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
+        <v>1</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>0.9991039704837336</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.0008960295162664</v>
       </c>
-      <c r="Y28" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -4461,19 +4622,19 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>1</v>
@@ -4482,116 +4643,122 @@
         <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9946928799393506</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0053008227881279</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>6.258363512196338e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.3589193369306667</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0375998109134493</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.015236516866304</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0128019006481698</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.027200090177287</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.540158346866936</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.0016313125206054</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0011612842157071</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0017852544252109</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0035061046310999</v>
       </c>
-      <c r="U29" t="n">
-        <v>1</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
       <c r="W29" t="n">
+        <v>1</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
         <v>0.999271923304172</v>
       </c>
-      <c r="X29" t="n">
+      <c r="Z29" t="n">
         <v>0.0007280766958278</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -4603,19 +4770,19 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="n">
         <v>1</v>
@@ -4624,84 +4791,90 @@
         <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.6443076758288035</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3556853348888049</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>6.9503733821338e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0016394532230402</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9959553800532482</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>2.655855161880552e-05</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>2.196724915476757e-08</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.153874512319122e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0023782745859198</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>2.611711692345883e-07</v>
       </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
@@ -4712,13 +4885,13 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4733,13 +4906,13 @@
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4751,137 +4924,143 @@
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
         <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
         <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9939755423848524</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0060171083580196</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>7.310348118806242e-06</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.4509450676984661</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.041596226187862</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0061913943467231</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>3.406728914579476e-06</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.4293166336268696</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>2.478279227694715e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.0719289199764928</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>4.057437931702466e-06</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>3.158748326909326e-06</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>8.618060175936824e-06</v>
       </c>
-      <c r="U31" t="n">
-        <v>1</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4893,13 +5072,13 @@
         <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO31" t="n">
         <v>1</v>
@@ -4908,122 +5087,128 @@
         <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9905139015308624</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0094793197786166</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>6.739781511802802e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.5258477203980684</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.3868617516982158</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>0.013254692704154</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>2.206275965528296e-06</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>5.111380230066542e-06</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>2.246328410452294e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.0728109237624408</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>3.502639273359253e-06</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>7.884621499431744e-06</v>
       </c>
-      <c r="T32" t="n">
+      <c r="V32" t="n">
         <v>0.0012039212827325</v>
       </c>
-      <c r="U32" t="n">
-        <v>1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5035,13 +5220,13 @@
         <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32" t="n">
         <v>1</v>
@@ -5050,116 +5235,122 @@
         <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.9863919826342769</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0136021390843382</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>5.839372375727016e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.3532184806271804</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.5592744851311984</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>1.221853528991591e-07</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0117894931120259</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.00209473975794</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.06277263009256601</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>2.314313282590097e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>1.874261577966895e-05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.0008186397114541</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>4.259636427251493e-06</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.0100060221857886</v>
       </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
       <c r="W33" t="n">
+        <v>1</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
         <v>0.2</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.8</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
       <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
         <v>0.9994536766782788</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.0005463233217211</v>
       </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -5171,19 +5362,19 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33" t="n">
         <v>1</v>
@@ -5192,116 +5383,122 @@
         <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
         <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.9845253570662552</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.0154689679693834</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>5.636055351881461e-06</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.3039445512970741</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.6033231939331323</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.0134408186035145</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0015720777986305</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0690518795982468</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>1.97185520030436e-06</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>4.518104327050857e-05</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>0.000552142436727</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>7.690228789292332e-06</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.008060402405563801</v>
       </c>
-      <c r="U34" t="n">
-        <v>1</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
       <c r="W34" t="n">
+        <v>1</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
         <v>0.2</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.8</v>
       </c>
-      <c r="Y34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -5313,19 +5510,19 @@
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK34" t="n">
         <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO34" t="n">
         <v>1</v>
@@ -5334,122 +5531,128 @@
         <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9874182876200615</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.01257593579756925</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>5.737673359925191e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.8978739355267571</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.02378719734210395</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.0296821059208284</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>1.088014653705349e-05</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.03029727227048175</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.0113939061493627</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.684263954863933e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.0069506658348803</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>2.347386621304573e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>1.53270667907711e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>5.461907431087323e-07</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.5</v>
       </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
         <v>0.2019329008855767</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.7980670991144233</v>
       </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
       <c r="AE35" t="n">
         <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5461,13 +5664,13 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="n">
         <v>1</v>
@@ -5476,116 +5679,122 @@
         <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
         <v>0</v>
       </c>
       <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9766840285992713</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0233102056541522</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>5.726837567246352e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.8744493082192958</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.0331003759827624</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.05937911465705695</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.01074790125921495</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.01139339846700345</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.0074482850402407</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>1.670533895001151e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.00337707364173825</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1.850793343665712e-06</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>1.841828956024458e-06</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>9.914066748336348e-05</v>
       </c>
-      <c r="U36" t="n">
+      <c r="W36" t="n">
         <v>0.5</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -5597,19 +5806,19 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO36" t="n">
         <v>1</v>
@@ -5618,116 +5827,122 @@
         <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
         <v>0</v>
       </c>
       <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9906699031436099</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.00932414134352785</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>5.916603852904126e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.6017147337606197</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.2995583913403231</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.05611676158934655</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.01706618553673835</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.0158038534545669</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.0066056728505106</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>2.278919277873619e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.0028963721419076</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>5.216546301567852e-06</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>2.575487735745703e-06</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.000227919463662541</v>
       </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
         <v>0.5</v>
       </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -5739,19 +5954,19 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="n">
         <v>1</v>
@@ -5760,116 +5975,122 @@
         <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
         <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9919245395380444</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.00806897234835985</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>6.449204586568105e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.2954563668587841</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.0444544436230301</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.0179409862768788</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.0262670357335158</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.0084149007929602</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.6044758878028397</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.000466877921746156</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>0.0001098983989223399</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.0021813283298682</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.0002322353524451</v>
       </c>
-      <c r="U38" t="n">
-        <v>1</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
+        <v>1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>0.999455782158991</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.0005442178410089001</v>
       </c>
-      <c r="Y38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -5881,19 +6102,19 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" t="n">
         <v>1</v>
@@ -5902,258 +6123,270 @@
         <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
         <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9942283651970449</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.005765097130243924</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>6.498763701987675e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.07995647234906135</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2193395231381966</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.01378861592711027</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.0081838233026186</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.02333377005339419</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.02686170286618115</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.6228356467426124</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.0004894447134925654</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.002187557070703325</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.0001567452407354645</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.00286665968688445</v>
       </c>
-      <c r="U39" t="n">
-        <v>1</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
       <c r="W39" t="n">
+        <v>1</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.749637801332948</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.00036219866705195</v>
       </c>
-      <c r="Y39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
       <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
         <v>0.1514537890296694</v>
       </c>
-      <c r="AB39" t="n">
+      <c r="AD39" t="n">
         <v>0.5985462109703306</v>
       </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
       <c r="AE39" t="n">
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>0.5</v>
       </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
       <c r="AL39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1</v>
-      </c>
       <c r="AP39" t="n">
         <v>0</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS39" t="n">
         <v>0</v>
       </c>
       <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9978572495788364</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.00213603922106455</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>6.672291089643319e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.1172346739295082</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.3945026707087697</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0107957895855029</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.0039001613500938</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.0109567487373629</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.0539547283650553</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.403990137437107</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>1.048675448470983e-05</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.0023988299153276</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>6.590804877995e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.0021898262589983</v>
       </c>
-      <c r="U40" t="n">
-        <v>1</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
       <c r="W40" t="n">
+        <v>1</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>0.4995460822542603</v>
       </c>
-      <c r="X40" t="n">
+      <c r="Z40" t="n">
         <v>0.0004539177457397</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
       <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
         <v>0.1009666931664185</v>
       </c>
-      <c r="AB40" t="n">
+      <c r="AD40" t="n">
         <v>0.3990333068335815</v>
       </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
       <c r="AE40" t="n">
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -6165,36 +6398,42 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>1</v>
-      </c>
       <c r="AP40" t="n">
         <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
       </c>
       <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>0.5</v>
       </c>
     </row>
